--- a/Database.xlsx
+++ b/Database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6112e55300fcb9f7/Documents/FL_Studio/Music/Pink_Noise/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="8_{261B944D-3154-41C4-A810-0FE7F57DCA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8334AE46-EA89-448E-89E2-8013D66A1A12}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="8_{261B944D-3154-41C4-A810-0FE7F57DCA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD1BD070-D791-4ADD-9749-41A294B75CBF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DFD942CF-3A3C-44FC-9CE1-5077A113D16C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="167">
   <si>
     <t>Artist</t>
   </si>
@@ -62,6 +62,9 @@
     <t>Paddy Mulcahy</t>
   </si>
   <si>
+    <t>www.paddymulcahy.com</t>
+  </si>
+  <si>
     <t>Melancholy Hill</t>
   </si>
   <si>
@@ -80,19 +83,28 @@
     <t>Cork</t>
   </si>
   <si>
+    <t>https://thesequiethours.ie</t>
+  </si>
+  <si>
     <t>Kateryna Horbenkova</t>
   </si>
   <si>
     <t>oootini</t>
   </si>
   <si>
+    <t>https://soundcloud.com/oootini</t>
+  </si>
+  <si>
     <t>Natalia Beylis</t>
   </si>
   <si>
     <t>Leitrim</t>
   </si>
   <si>
-    <t>Runs the Drumnadubber Artist Studios</t>
+    <t>https://nataliabeylis.bandcamp.com</t>
+  </si>
+  <si>
+    <t>Drumnadubber Artist Studios</t>
   </si>
   <si>
     <t>Last Eden</t>
@@ -104,9 +116,15 @@
     <t>Industrial</t>
   </si>
   <si>
+    <t>https://www.instagram.com/last__eden/</t>
+  </si>
+  <si>
     <t>Daire Lennon</t>
   </si>
   <si>
+    <t>https://dairelennon.com</t>
+  </si>
+  <si>
     <t>Roslyn Steer</t>
   </si>
   <si>
@@ -116,58 +134,70 @@
     <t>Péist</t>
   </si>
   <si>
+    <t>https://peist.bandcamp.com/</t>
+  </si>
+  <si>
     <t>Collective/Band</t>
   </si>
   <si>
     <t>Declan Synnott</t>
   </si>
   <si>
+    <t>https://declansynnott.bandcamp.com/</t>
+  </si>
+  <si>
+    <t>Tony Higgins</t>
+  </si>
+  <si>
+    <t>Agu</t>
+  </si>
+  <si>
+    <t>FurAngKa</t>
+  </si>
+  <si>
+    <t>Phil Maguire</t>
+  </si>
+  <si>
+    <t>https://philmaguire.com/</t>
+  </si>
+  <si>
+    <t>Solo</t>
+  </si>
+  <si>
+    <t>Jason Kahn</t>
+  </si>
+  <si>
+    <t>Zurich</t>
+  </si>
+  <si>
+    <t>Patrick Corcoran</t>
+  </si>
+  <si>
+    <t>https://patrickcorcoran.bandcamp.com/</t>
+  </si>
+  <si>
+    <t>Tony Monahan</t>
+  </si>
+  <si>
+    <t>www.tonymonahan.com</t>
+  </si>
+  <si>
+    <t>BB84</t>
+  </si>
+  <si>
+    <t>Nílim</t>
+  </si>
+  <si>
+    <t>Noise Metal</t>
+  </si>
+  <si>
+    <t>Black Coral</t>
+  </si>
+  <si>
     <t>Dublin</t>
   </si>
   <si>
-    <t>Aidan Reilly</t>
-  </si>
-  <si>
-    <t>Tony Higgins</t>
-  </si>
-  <si>
-    <t>Agu</t>
-  </si>
-  <si>
-    <t>FurAngKa</t>
-  </si>
-  <si>
-    <t>Phil Maguire</t>
-  </si>
-  <si>
-    <t>Scotland/Cork</t>
-  </si>
-  <si>
-    <t>Solo</t>
-  </si>
-  <si>
-    <t>Jason Kahn</t>
-  </si>
-  <si>
-    <t>Zurich</t>
-  </si>
-  <si>
-    <t>Patrick Corcoran</t>
-  </si>
-  <si>
-    <t>Tony Monahan</t>
-  </si>
-  <si>
-    <t>BB84</t>
-  </si>
-  <si>
-    <t>Nílim</t>
-  </si>
-  <si>
-    <t>Noise Metal</t>
-  </si>
-  <si>
-    <t>Black Coral</t>
+    <t>https://blackcoral23.bandcamp.com/</t>
   </si>
   <si>
     <t>Miss Foreign Affairs</t>
@@ -179,10 +209,13 @@
     <t>Therapy Horse</t>
   </si>
   <si>
+    <t>https://www.instagram.com/therapy.horse.ire</t>
+  </si>
+  <si>
     <t>WOLFBAIT</t>
   </si>
   <si>
-    <t>Kieran Kahoe</t>
+    <t>Kieran Kehoe</t>
   </si>
   <si>
     <t>Kilkenny</t>
@@ -194,18 +227,30 @@
     <t>Sine Tiler</t>
   </si>
   <si>
+    <t>https://sinetiler.bandcamp.com/</t>
+  </si>
+  <si>
     <t>Chris Ledwidge</t>
   </si>
   <si>
     <t>Lou McMahon</t>
   </si>
   <si>
+    <t>https://www.loumcmahon.ie/</t>
+  </si>
+  <si>
     <t>Mat Warren</t>
   </si>
   <si>
+    <t>https://www.matwarren.com</t>
+  </si>
+  <si>
     <t>Jonathan Crean</t>
   </si>
   <si>
+    <t>https://www.jonathancrean.com/</t>
+  </si>
+  <si>
     <t>White Sage</t>
   </si>
   <si>
@@ -215,12 +260,18 @@
     <t>barrelling+</t>
   </si>
   <si>
+    <t>https://barrelling.bandcamp.com/</t>
+  </si>
+  <si>
     <t>Aidan Thomas Tobin</t>
   </si>
   <si>
     <t>French Radio Constellation</t>
   </si>
   <si>
+    <t>https://frenchradioconstellation.bandcamp.com/</t>
+  </si>
+  <si>
     <t>Russell's Bogle</t>
   </si>
   <si>
@@ -284,6 +335,9 @@
     <t>Róisin Berg</t>
   </si>
   <si>
+    <t>https://roisinberg.art/</t>
+  </si>
+  <si>
     <t>Looming</t>
   </si>
   <si>
@@ -291,13 +345,205 @@
   </si>
   <si>
     <t>Dundalk</t>
+  </si>
+  <si>
+    <t>https://sonicwomb1.bandcamp.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jonathan Deasy </t>
+  </si>
+  <si>
+    <t>https://quietclapping.bandcamp.com</t>
+  </si>
+  <si>
+    <t>Ambient, Spoken Word</t>
+  </si>
+  <si>
+    <t>Ambient, Minimal Techno</t>
+  </si>
+  <si>
+    <t>https://less-air.github.io/orkid/about.html</t>
+  </si>
+  <si>
+    <t>Industrial, alternative rock</t>
+  </si>
+  <si>
+    <t>http://robinparmar.com/</t>
+  </si>
+  <si>
+    <t>https://melancholyhill.bandcamp.com/album/parts-of-me</t>
+  </si>
+  <si>
+    <t>Ambient, Drone, Noise</t>
+  </si>
+  <si>
+    <t>Ambient, Post-Rock</t>
+  </si>
+  <si>
+    <t>https://morespores.bandcamp.com/</t>
+  </si>
+  <si>
+    <t>Folk, Vocal, World Music</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kateryna.horbenkova/</t>
+  </si>
+  <si>
+    <t>Ambient, Drone</t>
+  </si>
+  <si>
+    <t>Avant-garde, musique concrete</t>
+  </si>
+  <si>
+    <t>Drone</t>
+  </si>
+  <si>
+    <t>https://roslynsteer.bandcamp.com/music</t>
+  </si>
+  <si>
+    <t>Folk</t>
+  </si>
+  <si>
+    <t>Minimal, leftfield</t>
+  </si>
+  <si>
+    <t>Improvisation, Noise</t>
+  </si>
+  <si>
+    <t>Noise</t>
+  </si>
+  <si>
+    <t>Ambient</t>
+  </si>
+  <si>
+    <t>https://junior85.bandcamp.com/music</t>
+  </si>
+  <si>
+    <t>https://agumusic.bandcamp.com/album/ke-sv-tlu</t>
+  </si>
+  <si>
+    <t>Czech Republic</t>
+  </si>
+  <si>
+    <t>https://furangka.bandcamp.com/music</t>
+  </si>
+  <si>
+    <t>Ambiente, Irish</t>
+  </si>
+  <si>
+    <t>https://jasonkahn.net/</t>
+  </si>
+  <si>
+    <t>Dublin, Leitrim</t>
+  </si>
+  <si>
+    <t>Avant-garde, Noise</t>
+  </si>
+  <si>
+    <t>https://bb84.bandcamp.com/album/ardnacrusha</t>
+  </si>
+  <si>
+    <t>https://nilim.neocities.org/</t>
+  </si>
+  <si>
+    <t>Drone, Noise, Ambient</t>
+  </si>
+  <si>
+    <t>Sligo, Barcelona</t>
+  </si>
+  <si>
+    <t>Avant-rock, Drone</t>
+  </si>
+  <si>
+    <t>https://owenkilfeather.bandcamp.com/music</t>
+  </si>
+  <si>
+    <t>Noise Rock, No Wave</t>
+  </si>
+  <si>
+    <t>Drone, Noise, Rock</t>
+  </si>
+  <si>
+    <t>https://wolfbaitcult.bandcamp.com/music</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kehoe.ceol/</t>
+  </si>
+  <si>
+    <t>https://arvq.bandcamp.com/track/n-os-l</t>
+  </si>
+  <si>
+    <t>Ambient, Downtempo</t>
+  </si>
+  <si>
+    <t>https://chrisledwidgemusic.com/</t>
+  </si>
+  <si>
+    <t>Ambient, Chamber</t>
+  </si>
+  <si>
+    <t>Drone, Contemporary, Minimalism</t>
+  </si>
+  <si>
+    <t>Ambient, Minimalism</t>
+  </si>
+  <si>
+    <t>Drone, Noise, Minimalism</t>
+  </si>
+  <si>
+    <t>Clare</t>
+  </si>
+  <si>
+    <t>Dark Ambiente, Downtempo</t>
+  </si>
+  <si>
+    <t>Dark ambient, Drone</t>
+  </si>
+  <si>
+    <t>Mayo</t>
+  </si>
+  <si>
+    <t>Electroacoustic, field recording</t>
+  </si>
+  <si>
+    <t>Psychedelic, Jazz</t>
+  </si>
+  <si>
+    <t>https://whitesage.bandcamp.com/music</t>
+  </si>
+  <si>
+    <t>https://marcaubele.bandcamp.com/music</t>
+  </si>
+  <si>
+    <t>Ambient, Microtonal</t>
+  </si>
+  <si>
+    <t>Ambient, Glitch, Noise</t>
+  </si>
+  <si>
+    <t>https://aidanthomastobin.com/</t>
+  </si>
+  <si>
+    <t>Rock, Punk</t>
+  </si>
+  <si>
+    <t>https://russellsbogle.bandcamp.com/music</t>
+  </si>
+  <si>
+    <t>Drone, Noise, Lo-fi</t>
+  </si>
+  <si>
+    <t>Jazz, Irish, Folk</t>
+  </si>
+  <si>
+    <t>https://sexytadhg.bandcamp.com/album/sluttrad</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -322,6 +568,14 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -340,18 +594,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -685,16 +942,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A5A2A8A-70C6-4D0F-949E-432942F6B4F0}">
   <dimension ref="A1:E63"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.5703125" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" customWidth="1"/>
+    <col min="3" max="3" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="54.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="55.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -711,428 +968,767 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="C2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="C3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="C5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="C6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="C8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>25</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>27</v>
+      </c>
+      <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" t="s">
+        <v>119</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="C14" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
         <v>6</v>
       </c>
+      <c r="C15" t="s">
+        <v>123</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="E15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
+        <v>124</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>36</v>
+      </c>
+      <c r="B17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" t="s">
+        <v>125</v>
+      </c>
+      <c r="D17" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>37</v>
+      </c>
+      <c r="B18" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" t="s">
+        <v>115</v>
+      </c>
+      <c r="D18" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>38</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
+        <v>130</v>
+      </c>
+      <c r="D19" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s">
+        <v>150</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" t="s">
+        <v>150</v>
+      </c>
+      <c r="D21" t="s">
+        <v>131</v>
+      </c>
+      <c r="E21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
+      <c r="C22" t="s">
+        <v>153</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" t="s">
+        <v>117</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" t="s">
         <v>33</v>
       </c>
-      <c r="B21" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" t="s">
-        <v>37</v>
-      </c>
-      <c r="E22" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>40</v>
-      </c>
-      <c r="E25" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>49</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B26" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="C26" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>136</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>137</v>
+      </c>
+      <c r="C27" t="s">
+        <v>138</v>
+      </c>
+      <c r="D27" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>14</v>
+      </c>
+      <c r="C28" t="s">
+        <v>140</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>52</v>
+      </c>
+      <c r="C29" t="s">
+        <v>141</v>
+      </c>
+      <c r="D29" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>59</v>
+      </c>
+      <c r="B30" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" t="s">
+        <v>149</v>
+      </c>
+      <c r="D30" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>55</v>
+      </c>
+      <c r="D31" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <v>52</v>
+      </c>
+      <c r="C32" t="s">
+        <v>145</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="B33" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="34" spans="1:2">
+      <c r="C33" t="s">
+        <v>147</v>
+      </c>
+      <c r="D33" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" t="s">
+        <v>151</v>
+      </c>
+      <c r="C34" t="s">
+        <v>148</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" t="s">
+        <v>152</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" t="s">
+        <v>154</v>
+      </c>
+      <c r="C36" t="s">
+        <v>155</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>55</v>
-      </c>
-      <c r="B37" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+      <c r="C37" t="s">
+        <v>156</v>
+      </c>
+      <c r="D37" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+        <v>72</v>
+      </c>
+      <c r="B38" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38" t="s">
+        <v>159</v>
+      </c>
+      <c r="D38" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <v>73</v>
+      </c>
+      <c r="B39" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" t="s">
+        <v>160</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>58</v>
-      </c>
-      <c r="B40" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+        <v>75</v>
+      </c>
+      <c r="C40" t="s">
+        <v>117</v>
+      </c>
+      <c r="D40" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+        <v>76</v>
+      </c>
+      <c r="B41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" t="s">
+        <v>162</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+        <v>78</v>
+      </c>
+      <c r="B42" t="s">
+        <v>52</v>
+      </c>
+      <c r="C42" t="s">
+        <v>164</v>
+      </c>
+      <c r="D42" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
+        <v>79</v>
+      </c>
+      <c r="B43" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43" t="s">
+        <v>165</v>
+      </c>
+      <c r="D43" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
+        <v>87</v>
+      </c>
+      <c r="B51" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>70</v>
-      </c>
-      <c r="B52" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
+        <v>95</v>
+      </c>
+      <c r="B58" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>78</v>
-      </c>
-      <c r="B59" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
+        <v>98</v>
+      </c>
+      <c r="B60" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="B61" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="B62" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
+        <v>102</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="B63" t="s">
-        <v>84</v>
+        <v>14</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{CCB55DC0-18EB-4D96-BE27-A4F9FDAF49A3}"/>
+    <hyperlink ref="D23" r:id="rId2" xr:uid="{5A37D94E-0373-4CA0-B757-1D732381263F}"/>
+    <hyperlink ref="D22" r:id="rId3" xr:uid="{5C11DED6-BB10-449D-9A82-6C2A6D838A11}"/>
+    <hyperlink ref="D34" r:id="rId4" xr:uid="{6E53BC9F-2191-4B50-BB4B-344BF739C495}"/>
+    <hyperlink ref="D35" r:id="rId5" xr:uid="{0162C932-5F31-4C42-AD7B-A877EF27CFBD}"/>
+    <hyperlink ref="D36" r:id="rId6" xr:uid="{06BDB73F-49D5-4446-AEF7-4BAF66CA62EC}"/>
+    <hyperlink ref="D11" r:id="rId7" xr:uid="{6A597E2D-F977-4F6A-B5FE-92B378EE8AE4}"/>
+    <hyperlink ref="D12" r:id="rId8" xr:uid="{7B0B3B19-2577-4516-9564-6626CFB0AE88}"/>
+    <hyperlink ref="D10" r:id="rId9" xr:uid="{4A0A1568-A229-43D7-88C1-C2C8F704672A}"/>
+    <hyperlink ref="D20" r:id="rId10" xr:uid="{75B784A1-60FB-487A-96AC-3666C9B126EF}"/>
+    <hyperlink ref="D16" r:id="rId11" xr:uid="{A822FF5E-B570-4882-88AC-0697ED866137}"/>
+    <hyperlink ref="D9" r:id="rId12" xr:uid="{EFC1DE87-6580-436F-AB42-96A494AF275B}"/>
+    <hyperlink ref="D62" r:id="rId13" xr:uid="{A89D8F21-645A-435D-91F6-08041B8ACE6A}"/>
+    <hyperlink ref="D60" r:id="rId14" xr:uid="{4B379C73-CE24-4C05-B083-C73BCF5BE915}"/>
+    <hyperlink ref="D41" r:id="rId15" xr:uid="{34486018-4237-4C25-B096-58C199032A86}"/>
+    <hyperlink ref="D39" r:id="rId16" xr:uid="{C512F059-B0DA-4081-9219-B1171DF277F9}"/>
+    <hyperlink ref="D15" r:id="rId17" xr:uid="{ED2B95DE-8D5D-453D-88A5-08A3574133D9}"/>
+    <hyperlink ref="D7" r:id="rId18" xr:uid="{1FC48E13-3B45-4841-A63F-814420BAB3D9}"/>
+    <hyperlink ref="D26" r:id="rId19" xr:uid="{EAB70F73-F452-464D-8494-D8313411AC87}"/>
+    <hyperlink ref="D28" r:id="rId20" xr:uid="{D1E15C48-D09F-42E5-A397-BAA1B22A37EA}"/>
+    <hyperlink ref="D32" r:id="rId21" xr:uid="{F4974A41-060A-4F82-AB87-57C0FA7149F5}"/>
+    <hyperlink ref="D63" r:id="rId22" xr:uid="{680916C5-961D-4B1B-956B-F2B7F8A44EEE}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Database.xlsx
+++ b/Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6112e55300fcb9f7/Documents/FL_Studio/Music/Pink_Noise/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="8_{261B944D-3154-41C4-A810-0FE7F57DCA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD1BD070-D791-4ADD-9749-41A294B75CBF}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="8_{261B944D-3154-41C4-A810-0FE7F57DCA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A53BA6D-812C-446E-BEE2-C2D5EC75AA1A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DFD942CF-3A3C-44FC-9CE1-5077A113D16C}"/>
   </bookViews>
@@ -434,9 +434,6 @@
     <t>https://jasonkahn.net/</t>
   </si>
   <si>
-    <t>Dublin, Leitrim</t>
-  </si>
-  <si>
     <t>Avant-garde, Noise</t>
   </si>
   <si>
@@ -449,9 +446,6 @@
     <t>Drone, Noise, Ambient</t>
   </si>
   <si>
-    <t>Sligo, Barcelona</t>
-  </si>
-  <si>
     <t>Avant-rock, Drone</t>
   </si>
   <si>
@@ -537,6 +531,12 @@
   </si>
   <si>
     <t>https://sexytadhg.bandcamp.com/album/sluttrad</t>
+  </si>
+  <si>
+    <t>Sligo/Barcelona</t>
+  </si>
+  <si>
+    <t>Dublin/Leitrim</t>
   </si>
 </sst>
 </file>
@@ -1246,7 +1246,7 @@
         <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>40</v>
@@ -1263,7 +1263,7 @@
         <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D21" t="s">
         <v>131</v>
@@ -1280,7 +1280,7 @@
         <v>6</v>
       </c>
       <c r="C22" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>45</v>
@@ -1305,13 +1305,13 @@
         <v>48</v>
       </c>
       <c r="B24" t="s">
+        <v>166</v>
+      </c>
+      <c r="C24" t="s">
         <v>132</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>133</v>
-      </c>
-      <c r="D24" t="s">
-        <v>134</v>
       </c>
       <c r="E24" t="s">
         <v>33</v>
@@ -1328,7 +1328,7 @@
         <v>50</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1339,7 +1339,7 @@
         <v>52</v>
       </c>
       <c r="C26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>53</v>
@@ -1350,13 +1350,13 @@
         <v>54</v>
       </c>
       <c r="B27" t="s">
+        <v>165</v>
+      </c>
+      <c r="C27" t="s">
+        <v>136</v>
+      </c>
+      <c r="D27" t="s">
         <v>137</v>
-      </c>
-      <c r="C27" t="s">
-        <v>138</v>
-      </c>
-      <c r="D27" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1367,7 +1367,7 @@
         <v>14</v>
       </c>
       <c r="C28" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>57</v>
@@ -1381,10 +1381,10 @@
         <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D29" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1395,10 +1395,10 @@
         <v>60</v>
       </c>
       <c r="C30" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D30" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1409,7 +1409,7 @@
         <v>55</v>
       </c>
       <c r="D31" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1420,7 +1420,7 @@
         <v>52</v>
       </c>
       <c r="C32" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>63</v>
@@ -1434,10 +1434,10 @@
         <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D33" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1445,10 +1445,10 @@
         <v>65</v>
       </c>
       <c r="B34" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C34" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>66</v>
@@ -1462,7 +1462,7 @@
         <v>20</v>
       </c>
       <c r="C35" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>68</v>
@@ -1473,10 +1473,10 @@
         <v>69</v>
       </c>
       <c r="B36" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C36" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>70</v>
@@ -1490,10 +1490,10 @@
         <v>52</v>
       </c>
       <c r="C37" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D37" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1504,10 +1504,10 @@
         <v>52</v>
       </c>
       <c r="C38" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D38" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1518,7 +1518,7 @@
         <v>52</v>
       </c>
       <c r="C39" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>74</v>
@@ -1532,7 +1532,7 @@
         <v>117</v>
       </c>
       <c r="D40" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1543,7 +1543,7 @@
         <v>52</v>
       </c>
       <c r="C41" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>77</v>
@@ -1557,10 +1557,10 @@
         <v>52</v>
       </c>
       <c r="C42" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D42" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1571,10 +1571,10 @@
         <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D43" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">

--- a/Database.xlsx
+++ b/Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6112e55300fcb9f7/Documents/FL_Studio/Music/Pink_Noise/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="8_{261B944D-3154-41C4-A810-0FE7F57DCA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A53BA6D-812C-446E-BEE2-C2D5EC75AA1A}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="8_{261B944D-3154-41C4-A810-0FE7F57DCA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9338D05A-CDA1-47C1-9304-69F53E583602}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DFD942CF-3A3C-44FC-9CE1-5077A113D16C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="199">
   <si>
     <t>Artist</t>
   </si>
@@ -537,6 +537,102 @@
   </si>
   <si>
     <t>Dublin/Leitrim</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=PFQxurQFcAE</t>
+  </si>
+  <si>
+    <t>Electroacoustic, Glitch</t>
+  </si>
+  <si>
+    <t>Ambient, Vocal</t>
+  </si>
+  <si>
+    <t>https://kcnmusic1.bandcamp.com/music</t>
+  </si>
+  <si>
+    <t>https://www.katie-oneill.com/</t>
+  </si>
+  <si>
+    <t>Ambient, Field recording, Noise</t>
+  </si>
+  <si>
+    <t>https://alfa00.bandcamp.com/audio</t>
+  </si>
+  <si>
+    <t>https://caitin.bandcamp.com/music</t>
+  </si>
+  <si>
+    <t>Folk, Irish</t>
+  </si>
+  <si>
+    <t>Ambient, Vaporwave</t>
+  </si>
+  <si>
+    <t>https://mk1recordings.bandcamp.com/</t>
+  </si>
+  <si>
+    <t>https://assemblylinemusic.bandcamp.com/music</t>
+  </si>
+  <si>
+    <t>https://conchr.bandcamp.com/music</t>
+  </si>
+  <si>
+    <t>Ambient, Chillwave</t>
+  </si>
+  <si>
+    <t>https://www.subvert.fm/29fs</t>
+  </si>
+  <si>
+    <t>Drone, Americana</t>
+  </si>
+  <si>
+    <t>Ambient, Folk</t>
+  </si>
+  <si>
+    <t>https://strandunit.bandcamp.com/music</t>
+  </si>
+  <si>
+    <t>https://lifewing.bandcamp.com/music</t>
+  </si>
+  <si>
+    <t>Bristol</t>
+  </si>
+  <si>
+    <t>Ambient, Noise, Drone</t>
+  </si>
+  <si>
+    <t>https://colinjameswoods.com/</t>
+  </si>
+  <si>
+    <t>Ambient, IDM</t>
+  </si>
+  <si>
+    <t>https://mickchillage.bandcamp.com/</t>
+  </si>
+  <si>
+    <t>Ambient, Jazz</t>
+  </si>
+  <si>
+    <t>https://www.subvert.fm/maverick</t>
+  </si>
+  <si>
+    <t>https://oceanfloor.bandcamp.com/music</t>
+  </si>
+  <si>
+    <t>Ambient, Drone, Minimalism</t>
+  </si>
+  <si>
+    <t>Ambient, Techno</t>
+  </si>
+  <si>
+    <t>https://dubdelay1.bandcamp.com/music</t>
+  </si>
+  <si>
+    <t>Ambient, Noise, Drone, Industrial</t>
+  </si>
+  <si>
+    <t>Electroacoustic, Minimalism, Drone</t>
   </si>
 </sst>
 </file>
@@ -946,7 +1042,7 @@
   <cols>
     <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.5703125" customWidth="1"/>
-    <col min="3" max="3" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="54.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="55.42578125" customWidth="1"/>
   </cols>
@@ -1408,6 +1504,9 @@
       <c r="B31" t="s">
         <v>55</v>
       </c>
+      <c r="C31" t="s">
+        <v>169</v>
+      </c>
       <c r="D31" t="s">
         <v>142</v>
       </c>
@@ -1586,31 +1685,79 @@
       <c r="A45" t="s">
         <v>81</v>
       </c>
+      <c r="B45" t="s">
+        <v>52</v>
+      </c>
+      <c r="C45" t="s">
+        <v>124</v>
+      </c>
+      <c r="D45" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>82</v>
       </c>
+      <c r="B46" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46" t="s">
+        <v>172</v>
+      </c>
+      <c r="D46" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>83</v>
       </c>
+      <c r="B47" t="s">
+        <v>149</v>
+      </c>
+      <c r="C47" t="s">
+        <v>172</v>
+      </c>
+      <c r="D47" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>84</v>
       </c>
+      <c r="C48" t="s">
+        <v>175</v>
+      </c>
+      <c r="D48" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>85</v>
       </c>
+      <c r="B49" t="s">
+        <v>52</v>
+      </c>
+      <c r="C49" t="s">
+        <v>176</v>
+      </c>
+      <c r="D49" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>86</v>
       </c>
+      <c r="C50" t="s">
+        <v>143</v>
+      </c>
+      <c r="D50" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
@@ -1619,36 +1766,93 @@
       <c r="B51" t="s">
         <v>88</v>
       </c>
+      <c r="C51" t="s">
+        <v>180</v>
+      </c>
+      <c r="D51" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>89</v>
       </c>
+      <c r="B52" t="s">
+        <v>88</v>
+      </c>
+      <c r="C52" t="s">
+        <v>182</v>
+      </c>
+      <c r="D52" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>90</v>
       </c>
+      <c r="B53" t="s">
+        <v>52</v>
+      </c>
+      <c r="C53" t="s">
+        <v>183</v>
+      </c>
+      <c r="D53" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>91</v>
       </c>
+      <c r="B54" t="s">
+        <v>186</v>
+      </c>
+      <c r="C54" t="s">
+        <v>125</v>
+      </c>
+      <c r="D54" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>92</v>
       </c>
+      <c r="B55" t="s">
+        <v>88</v>
+      </c>
+      <c r="C55" t="s">
+        <v>187</v>
+      </c>
+      <c r="D55" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>93</v>
       </c>
+      <c r="B56" t="s">
+        <v>52</v>
+      </c>
+      <c r="C56" t="s">
+        <v>189</v>
+      </c>
+      <c r="D56" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>94</v>
       </c>
+      <c r="C57" t="s">
+        <v>191</v>
+      </c>
+      <c r="D57" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
@@ -1657,11 +1861,26 @@
       <c r="B58" t="s">
         <v>96</v>
       </c>
+      <c r="C58" t="s">
+        <v>194</v>
+      </c>
+      <c r="D58" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>97</v>
       </c>
+      <c r="B59" t="s">
+        <v>52</v>
+      </c>
+      <c r="C59" t="s">
+        <v>195</v>
+      </c>
+      <c r="D59" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
@@ -1670,6 +1889,9 @@
       <c r="B60" t="s">
         <v>6</v>
       </c>
+      <c r="C60" t="s">
+        <v>124</v>
+      </c>
       <c r="D60" s="4" t="s">
         <v>99</v>
       </c>
@@ -1681,6 +1903,12 @@
       <c r="B61" t="s">
         <v>6</v>
       </c>
+      <c r="C61" t="s">
+        <v>168</v>
+      </c>
+      <c r="D61" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
@@ -1689,6 +1917,9 @@
       <c r="B62" t="s">
         <v>102</v>
       </c>
+      <c r="C62" t="s">
+        <v>197</v>
+      </c>
       <c r="D62" s="4" t="s">
         <v>103</v>
       </c>
@@ -1699,6 +1930,9 @@
       </c>
       <c r="B63" t="s">
         <v>14</v>
+      </c>
+      <c r="C63" t="s">
+        <v>198</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>105</v>
